--- a/data/dividends_info_20260418.xlsx
+++ b/data/dividends_info_20260418.xlsx
@@ -8724,7 +8724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C638"/>
+  <dimension ref="A1:C628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9733,7 +9733,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -9750,7 +9750,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -9784,7 +9784,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -9801,7 +9801,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -9886,7 +9886,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -10022,7 +10022,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10039,7 +10039,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -10049,14 +10049,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10066,14 +10066,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10107,7 +10107,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10117,14 +10117,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10141,7 +10141,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10158,7 +10158,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10168,14 +10168,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10192,7 +10192,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10202,14 +10202,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10219,14 +10219,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10243,7 +10243,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10260,7 +10260,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10277,7 +10277,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10287,14 +10287,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10304,14 +10304,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10321,14 +10321,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10338,14 +10338,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10362,7 +10362,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10372,14 +10372,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10396,7 +10396,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10413,7 +10413,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10430,7 +10430,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10447,7 +10447,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10464,7 +10464,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10498,7 +10498,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -10549,7 +10549,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10617,7 +10617,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10634,7 +10634,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10651,7 +10651,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10668,7 +10668,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10678,14 +10678,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10702,7 +10702,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10719,7 +10719,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10736,7 +10736,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10753,7 +10753,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10770,7 +10770,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10787,7 +10787,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10797,14 +10797,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10821,7 +10821,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10838,7 +10838,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10855,7 +10855,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10889,7 +10889,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10906,7 +10906,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10923,7 +10923,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10940,7 +10940,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10957,7 +10957,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10974,7 +10974,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10991,7 +10991,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11008,7 +11008,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11025,7 +11025,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11042,7 +11042,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11059,7 +11059,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11076,7 +11076,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11093,7 +11093,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11110,7 +11110,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11127,7 +11127,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11137,14 +11137,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11154,14 +11154,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11178,7 +11178,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11195,7 +11195,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11212,7 +11212,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11229,7 +11229,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11246,7 +11246,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11263,7 +11263,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11280,7 +11280,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11290,14 +11290,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11314,7 +11314,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11331,7 +11331,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11348,7 +11348,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11365,7 +11365,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11382,7 +11382,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11399,7 +11399,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11416,7 +11416,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11433,7 +11433,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11450,7 +11450,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11467,7 +11467,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11484,7 +11484,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11501,7 +11501,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11518,7 +11518,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11528,14 +11528,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11545,14 +11545,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11569,7 +11569,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11586,7 +11586,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11603,7 +11603,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11654,7 +11654,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11671,7 +11671,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11688,7 +11688,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11698,14 +11698,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11722,7 +11722,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11739,7 +11739,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11756,7 +11756,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11766,14 +11766,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11790,7 +11790,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11800,14 +11800,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11824,7 +11824,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11841,7 +11841,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11858,7 +11858,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11875,7 +11875,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11892,7 +11892,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11902,14 +11902,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11926,7 +11926,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11943,7 +11943,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11960,7 +11960,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11977,7 +11977,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11994,7 +11994,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12011,7 +12011,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12028,7 +12028,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12045,7 +12045,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12062,7 +12062,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12079,7 +12079,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12096,7 +12096,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12113,7 +12113,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12123,14 +12123,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12147,7 +12147,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12164,7 +12164,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12181,7 +12181,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12232,7 +12232,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12249,7 +12249,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12266,7 +12266,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12276,14 +12276,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12300,7 +12300,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12317,7 +12317,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12334,7 +12334,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12344,14 +12344,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12368,7 +12368,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12378,14 +12378,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12402,7 +12402,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12419,7 +12419,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12429,14 +12429,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12446,14 +12446,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12470,7 +12470,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12487,7 +12487,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12504,7 +12504,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12521,7 +12521,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12538,7 +12538,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12555,7 +12555,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12572,7 +12572,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12589,7 +12589,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12599,14 +12599,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12616,14 +12616,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12640,7 +12640,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12657,7 +12657,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12674,7 +12674,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12684,14 +12684,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12708,7 +12708,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12718,14 +12718,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12742,7 +12742,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12759,7 +12759,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12776,7 +12776,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12786,14 +12786,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12810,7 +12810,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12827,7 +12827,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -12844,7 +12844,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12861,7 +12861,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12878,7 +12878,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12888,14 +12888,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12905,14 +12905,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -12929,7 +12929,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -12946,7 +12946,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -12956,14 +12956,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -12980,7 +12980,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -12990,14 +12990,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13014,7 +13014,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13031,7 +13031,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13041,14 +13041,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13065,7 +13065,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13082,7 +13082,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13099,7 +13099,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13116,7 +13116,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13133,7 +13133,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13150,7 +13150,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13167,7 +13167,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13184,7 +13184,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13194,14 +13194,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13218,7 +13218,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -13228,14 +13228,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -13245,14 +13245,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -13262,14 +13262,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -13279,14 +13279,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -13296,14 +13296,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13320,7 +13320,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13337,7 +13337,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13354,7 +13354,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13371,7 +13371,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -13388,7 +13388,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13405,7 +13405,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -13415,14 +13415,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13439,7 +13439,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13456,7 +13456,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13473,7 +13473,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13483,14 +13483,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13507,7 +13507,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13524,7 +13524,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13541,7 +13541,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13558,7 +13558,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13575,7 +13575,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13592,7 +13592,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13609,7 +13609,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13626,7 +13626,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13643,7 +13643,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13653,14 +13653,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13677,7 +13677,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13694,7 +13694,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13704,14 +13704,14 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13721,14 +13721,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13738,14 +13738,14 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13762,7 +13762,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13772,14 +13772,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13789,14 +13789,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13813,7 +13813,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -13823,14 +13823,14 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13840,14 +13840,14 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -13864,7 +13864,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -13881,7 +13881,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -13891,14 +13891,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -13915,7 +13915,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -13932,7 +13932,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -13949,7 +13949,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -13966,7 +13966,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -13983,7 +13983,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -14000,7 +14000,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -14010,14 +14010,14 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -14034,7 +14034,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -14051,7 +14051,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -14068,7 +14068,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -14085,7 +14085,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14102,7 +14102,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14112,14 +14112,14 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -14136,7 +14136,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -14153,7 +14153,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14170,7 +14170,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14180,14 +14180,14 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14204,7 +14204,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14221,7 +14221,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14238,7 +14238,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14248,14 +14248,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14272,7 +14272,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14289,7 +14289,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14306,7 +14306,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14323,7 +14323,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14340,7 +14340,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14357,7 +14357,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14367,14 +14367,14 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14384,14 +14384,14 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14408,7 +14408,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14425,7 +14425,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14442,7 +14442,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14459,7 +14459,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -14476,7 +14476,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14493,7 +14493,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -14510,7 +14510,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -14527,7 +14527,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -14544,7 +14544,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -14561,7 +14561,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -14571,14 +14571,14 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -14595,7 +14595,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -14612,7 +14612,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -14629,7 +14629,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -14646,7 +14646,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -14656,14 +14656,14 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -14680,7 +14680,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -14697,7 +14697,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -14714,7 +14714,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -14731,7 +14731,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -14748,7 +14748,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -14765,7 +14765,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -14782,7 +14782,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -14833,7 +14833,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -14843,14 +14843,14 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -14867,7 +14867,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -14884,7 +14884,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -14894,14 +14894,14 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -14911,14 +14911,14 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -14935,7 +14935,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -14945,14 +14945,14 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -14969,7 +14969,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -14979,14 +14979,14 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -15003,7 +15003,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -15013,14 +15013,14 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -15030,14 +15030,14 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -15054,7 +15054,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -15071,7 +15071,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -15088,7 +15088,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -15105,7 +15105,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -15122,7 +15122,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -15139,7 +15139,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -15156,7 +15156,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -15166,14 +15166,14 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -15183,14 +15183,14 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -15200,14 +15200,14 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -15217,14 +15217,14 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -15241,7 +15241,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -15258,7 +15258,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -15268,14 +15268,14 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -15292,7 +15292,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -15302,14 +15302,14 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -15319,14 +15319,14 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -15343,7 +15343,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -15353,14 +15353,14 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -15370,14 +15370,14 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -15387,14 +15387,14 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -15404,14 +15404,14 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -15421,14 +15421,14 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -15438,14 +15438,14 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -15455,14 +15455,14 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -15472,14 +15472,14 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -15489,14 +15489,14 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -15506,14 +15506,14 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -15530,7 +15530,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -15547,7 +15547,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -15564,7 +15564,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -15581,7 +15581,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -15598,7 +15598,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -15615,7 +15615,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -15625,14 +15625,14 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -15642,14 +15642,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -15666,7 +15666,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -15683,7 +15683,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15700,7 +15700,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -15717,7 +15717,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -15727,14 +15727,14 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -15751,7 +15751,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -15768,7 +15768,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -15778,14 +15778,14 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -15795,14 +15795,14 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -15819,7 +15819,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -15836,7 +15836,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -15846,14 +15846,14 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -15863,7 +15863,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -15887,12 +15887,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -15904,29 +15904,29 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -15938,12 +15938,12 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -15955,29 +15955,29 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -15989,12 +15989,12 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -16006,58 +16006,58 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -16067,14 +16067,14 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -16091,7 +16091,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -16101,14 +16101,14 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -16125,7 +16125,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -16135,14 +16135,14 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -16159,7 +16159,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -16169,14 +16169,14 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -16186,14 +16186,14 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -16203,14 +16203,14 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -16220,14 +16220,14 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -16237,14 +16237,14 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -16254,14 +16254,14 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -16271,14 +16271,14 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -16288,14 +16288,14 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -16305,14 +16305,14 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -16329,7 +16329,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -16346,7 +16346,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -16363,7 +16363,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -16373,14 +16373,14 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -16390,14 +16390,14 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -16407,14 +16407,14 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -16424,14 +16424,14 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -16441,14 +16441,14 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -16458,14 +16458,14 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -16475,14 +16475,14 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -16492,14 +16492,14 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -16509,14 +16509,14 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -16526,14 +16526,14 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -16543,14 +16543,14 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -16560,14 +16560,14 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -16584,7 +16584,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -16601,7 +16601,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -16618,7 +16618,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -16628,14 +16628,14 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -16645,19 +16645,19 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -16669,46 +16669,46 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -16720,12 +16720,12 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -16737,12 +16737,12 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -16754,75 +16754,75 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -16832,19 +16832,19 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -16856,12 +16856,12 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -16873,29 +16873,29 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -16907,12 +16907,12 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -16924,29 +16924,29 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -16958,29 +16958,29 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -16992,29 +16992,29 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -17026,29 +17026,29 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -17060,12 +17060,12 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -17077,29 +17077,29 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -17111,12 +17111,12 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -17128,12 +17128,12 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -17145,41 +17145,41 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -17196,7 +17196,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -17206,14 +17206,14 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -17223,14 +17223,14 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -17240,14 +17240,14 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -17257,14 +17257,14 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -17274,14 +17274,14 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -17298,7 +17298,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -17308,14 +17308,14 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -17325,14 +17325,14 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -17349,7 +17349,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -17359,14 +17359,14 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -17376,14 +17376,14 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -17400,7 +17400,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -17410,14 +17410,14 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -17427,14 +17427,14 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -17444,14 +17444,14 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -17468,46 +17468,46 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -17519,12 +17519,12 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -17536,29 +17536,29 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -17570,46 +17570,46 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -17621,24 +17621,24 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -17655,7 +17655,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -17665,14 +17665,14 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -17689,7 +17689,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -17723,7 +17723,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -17733,14 +17733,14 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -17757,7 +17757,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -17767,14 +17767,14 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -17784,14 +17784,14 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -17801,14 +17801,14 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17825,7 +17825,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -17835,14 +17835,14 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -17859,7 +17859,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -17876,7 +17876,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -17886,14 +17886,14 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -17903,14 +17903,14 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -17927,7 +17927,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -17937,14 +17937,14 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -17961,7 +17961,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -17971,14 +17971,14 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -18012,7 +18012,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -18022,14 +18022,14 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -18046,7 +18046,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -18056,14 +18056,14 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -18073,36 +18073,36 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -18114,29 +18114,29 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -18148,63 +18148,63 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -18216,29 +18216,29 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -18250,7 +18250,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -18260,14 +18260,14 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -18284,7 +18284,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -18301,7 +18301,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -18311,14 +18311,14 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -18335,7 +18335,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -18352,7 +18352,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -18369,7 +18369,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -18386,7 +18386,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -18403,7 +18403,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -18420,7 +18420,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -18430,14 +18430,14 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -18454,7 +18454,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -18471,7 +18471,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -18481,14 +18481,14 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -18505,7 +18505,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -18522,7 +18522,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -18539,7 +18539,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -18549,14 +18549,14 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -18573,7 +18573,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -18590,7 +18590,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -18600,14 +18600,14 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -18624,7 +18624,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -18634,14 +18634,14 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -18651,14 +18651,14 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -18675,7 +18675,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -18692,7 +18692,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -18709,7 +18709,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -18719,14 +18719,14 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -18736,14 +18736,14 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -18760,7 +18760,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -18777,7 +18777,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -18794,7 +18794,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -18804,14 +18804,14 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -18828,7 +18828,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -18838,7 +18838,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -18862,7 +18862,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -18872,14 +18872,14 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -18889,14 +18889,14 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -18913,7 +18913,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -18923,14 +18923,14 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -18940,19 +18940,19 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -18964,12 +18964,12 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -18981,29 +18981,29 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -19015,29 +19015,29 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -19049,46 +19049,46 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -19100,12 +19100,12 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -19117,7 +19117,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -19134,7 +19134,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -19144,14 +19144,14 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -19161,14 +19161,14 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -19185,7 +19185,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -19253,7 +19253,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -19287,7 +19287,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -19297,14 +19297,14 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -19321,7 +19321,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -19331,36 +19331,36 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -19372,12 +19372,12 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -19389,187 +19389,17 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
           <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
-        <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B629" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C629" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
-        <is>
-          <t>VNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B630" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C630" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
-        <is>
-          <t>GVS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B631" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C631" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
-        <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B632" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C632" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
-        <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B633" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C633" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
-        <is>
-          <t>VNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B634" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C634" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
-        <is>
-          <t>OMER S.p.A.</t>
-        </is>
-      </c>
-      <c r="B635" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="C635" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
-        <is>
-          <t>GREEN OLEO S.p.A</t>
-        </is>
-      </c>
-      <c r="B636" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="C636" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
-        <is>
-          <t>EuroGroup Laminations S.p.A.</t>
-        </is>
-      </c>
-      <c r="B637" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="C637" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
-        <is>
-          <t>BESTBE HOLDING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B638" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="C638" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -19597,95 +19427,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BESTBE HOLDING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>EuroGroup Laminations S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>GREEN OLEO S.p.A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>OMER S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>